--- a/data/trans_dic/IQ2608_R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IQ2608_R3-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>71,57%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>81,02%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>87,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>57,35%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>67,38%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>81,3%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>82,99%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>83,37%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>71,57%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>81,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>87,0%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>64,94%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>59,57; 76,45</t>
+          <t>63,03; 78,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73,92; 87,47</t>
+          <t>72,01; 87,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73,2; 89,84</t>
+          <t>79,03; 92,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59,61; 97,67</t>
+          <t>33,28; 78,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>63,41; 78,83</t>
+          <t>58,8; 75,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,56; 87,34</t>
+          <t>74,44; 87,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,97; 92,66</t>
+          <t>74,87; 89,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,11; 81,42</t>
+          <t>45,89; 95,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>63,86; 75,0</t>
+          <t>63,81; 75,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75,67; 85,84</t>
+          <t>76,03; 85,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79,55; 90,02</t>
+          <t>79,82; 89,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,15; 85,02</t>
+          <t>46,0; 80,58</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>60,71%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>80,47%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83,24%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68,43%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>59,7%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>79,16%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>80,25%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>62,43%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>60,71%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>80,47%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>83,24%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>65,74%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,61; 63,45</t>
+          <t>57,26; 64,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>75,99; 82,37</t>
+          <t>77,64; 83,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,08; 83,1</t>
+          <t>80,22; 85,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53,66; 70,83</t>
+          <t>61,13; 76,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>56,99; 64,01</t>
+          <t>55,74; 63,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,53; 83,66</t>
+          <t>75,91; 82,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,39; 85,91</t>
+          <t>77,01; 82,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>60,72; 76,32</t>
+          <t>53,64; 70,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57,93; 63,07</t>
+          <t>57,56; 62,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77,63; 82,02</t>
+          <t>77,51; 81,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79,74; 83,81</t>
+          <t>79,57; 83,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>60,59; 71,95</t>
+          <t>60,09; 71,08</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>67,66%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>86,19%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>81,85%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>71,39%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>59,12%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>85,28%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>80,36%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>65,96%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>67,66%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,85%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,33%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53,1; 65,71</t>
+          <t>62,09; 73,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,96; 89,62</t>
+          <t>81,19; 89,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75,05; 84,87</t>
+          <t>76,5; 86,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54,45; 77,26</t>
+          <t>56,97; 82,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60,98; 73,46</t>
+          <t>53,28; 65,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,17; 90,25</t>
+          <t>80,26; 89,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,68; 86,31</t>
+          <t>74,98; 85,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>57,09; 82,21</t>
+          <t>53,61; 76,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>58,8; 67,18</t>
+          <t>58,64; 67,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>82,28; 88,51</t>
+          <t>82,15; 88,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77,27; 84,28</t>
+          <t>77,09; 84,14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59,37; 76,73</t>
+          <t>58,92; 77,26</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>63,52%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>81,82%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>83,25%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>68,37%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>60,58%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>80,86%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>80,51%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>65,14%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>63,52%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>81,82%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>83,25%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,39%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,54; 63,48</t>
+          <t>60,74; 66,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,45; 83,3</t>
+          <t>79,13; 84,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,02; 82,81</t>
+          <t>80,85; 85,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58,15; 71,23</t>
+          <t>61,81; 74,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>60,91; 66,53</t>
+          <t>57,64; 63,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,5; 84,1</t>
+          <t>78,13; 83,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,0; 85,6</t>
+          <t>77,95; 82,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>62,76; 75,49</t>
+          <t>56,85; 70,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>59,81; 64,09</t>
+          <t>60,01; 64,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79,63; 83,05</t>
+          <t>79,48; 83,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80,28; 83,54</t>
+          <t>80,34; 83,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,92; 72,15</t>
+          <t>61,44; 70,9</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1373,37 +1373,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>60307</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>69322</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>59691</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7108</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>59921</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>73264</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>48805</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9384</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>60307</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>69322</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>59691</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17923</t>
+          <t>13438</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>52975; 67985</t>
+          <t>53115; 66463</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>66616; 78831</t>
+          <t>61616; 74775</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43048; 52834</t>
+          <t>54223; 63792</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6710; 10994</t>
+          <t>4125; 9717</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>53431; 66425</t>
+          <t>52291; 67057</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62941; 74732</t>
+          <t>67086; 78700</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54186; 63579</t>
+          <t>44031; 52575</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4993; 11259</t>
+          <t>3809; 7943</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>110593; 129899</t>
+          <t>110512; 129981</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>132933; 150803</t>
+          <t>133569; 150705</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>101358; 114709</t>
+          <t>101706; 114506</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13333; 21327</t>
+          <t>9519; 16675</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>369</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>502</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>568</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>88</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>576</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>284598</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>383385</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>404954</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>84090</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>242642</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>347852</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>373872</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>55307</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>284598</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>383385</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>404954</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>92238</t>
+          <t>54267</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>147546</t>
+          <t>138357</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>226003; 257863</t>
+          <t>268427; 302585</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>333922; 361933</t>
+          <t>369913; 396562</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>359089; 387121</t>
+          <t>390277; 417514</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47540; 62747</t>
+          <t>75125; 93814</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>267151; 300056</t>
+          <t>226532; 258517</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>369394; 398607</t>
+          <t>333545; 361264</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>391081; 417965</t>
+          <t>358774; 386313</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80884; 101670</t>
+          <t>46977; 61959</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>506981; 551958</t>
+          <t>503784; 548014</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>710975; 751179</t>
+          <t>709879; 750689</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>759387; 798157</t>
+          <t>757758; 795938</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>134391; 159599</t>
+          <t>126479; 149598</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>193</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>46</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>103881</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>140871</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>149151</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>30759</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>100110</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>136616</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>135691</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>28525</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>103881</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>140871</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>149151</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31731</t>
+          <t>28509</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60256</t>
+          <t>59267</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>89907; 111268</t>
+          <t>95326; 113256</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>128088; 143556</t>
+          <t>132689; 146981</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126733; 143319</t>
+          <t>139409; 156861</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23549; 33412</t>
+          <t>24547; 35486</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>93623; 112777</t>
+          <t>90212; 110363</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>132666; 147507</t>
+          <t>128559; 143672</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>139729; 157276</t>
+          <t>126604; 143755</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25533; 36765</t>
+          <t>23402; 33612</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>189834; 216886</t>
+          <t>189304; 218588</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>266276; 286452</t>
+          <t>265862; 287291</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>271270; 295885</t>
+          <t>270651; 295415</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>52229; 67498</t>
+          <t>51107; 67017</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>878</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>606</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>801</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>845</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>146</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>844</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>878</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>448785</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>593578</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>613797</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>121957</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>402674</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>557731</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>558368</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>93216</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>448785</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>593578</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>613797</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>132508</t>
+          <t>89106</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>225724</t>
+          <t>211062</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>382463; 421897</t>
+          <t>429185; 469225</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>541099; 574532</t>
+          <t>574065; 609699</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>541123; 574331</t>
+          <t>596134; 629014</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83202; 101927</t>
+          <t>110250; 133410</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>430323; 470060</t>
+          <t>383130; 422022</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>576754; 610092</t>
+          <t>538893; 573373</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>597211; 631168</t>
+          <t>540588; 573493</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>120350; 144765</t>
+          <t>79324; 97910</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>820057; 878872</t>
+          <t>822803; 880336</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1126911; 1175280</t>
+          <t>1124778; 1175478</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1148659; 1195316</t>
+          <t>1149605; 1195652</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>210701; 241588</t>
+          <t>195323; 225383</t>
         </is>
       </c>
     </row>
